--- a/Metadata.xlsx
+++ b/Metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Phd\My works\1. CAE_HWJ\Manuscript\手稿\18. CAE_Hwj_Manuscript_v18_2024.08.10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Phd\My works\1. CAE_HWJ\Manuscript\投稿\2. GBC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCD8283-2EA2-441D-AB15-17B0C6BBA889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363FB2A1-85FA-4F23-A726-350B1FADBEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Meta" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="CUE" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CUE!$A$1:$N$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CUE!$A$1:$N$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="81">
   <si>
     <t>No.</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>forest</t>
-  </si>
-  <si>
-    <t>Brant et al 2006</t>
   </si>
   <si>
     <t>Qiao et al 2014</t>
@@ -737,150 +734,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.9140625" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C14" s="1"/>
     </row>
@@ -892,20 +889,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5DCC57-A8E7-4674-8C7A-B9B0FDBD20D8}">
-  <dimension ref="A1:N208"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N204"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="4" width="8.88671875" style="7"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="10" width="8.88671875" style="7"/>
-    <col min="11" max="11" width="8.88671875" style="10"/>
-    <col min="12" max="12" width="8.88671875" style="1"/>
-    <col min="13" max="13" width="8.88671875" style="7"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="2" width="8.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.9140625" style="7"/>
+    <col min="5" max="5" width="8.9140625" style="1"/>
+    <col min="6" max="10" width="8.9140625" style="7"/>
+    <col min="11" max="11" width="8.9140625" style="10"/>
+    <col min="12" max="12" width="8.9140625" style="1"/>
+    <col min="13" max="13" width="8.9140625" style="7"/>
+    <col min="14" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -922,7 +919,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>5</v>
@@ -931,7 +928,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>7</v>
@@ -946,10 +943,10 @@
         <v>10</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -993,7 +990,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -1037,7 +1034,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1081,7 +1078,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1125,7 +1122,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1169,7 +1166,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -1213,7 +1210,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1257,7 +1254,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1301,7 +1298,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -1345,7 +1342,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -1389,7 +1386,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1433,7 +1430,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -1477,7 +1474,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -1521,7 +1518,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1565,7 +1562,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2</v>
       </c>
@@ -1609,7 +1606,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>2</v>
       </c>
@@ -1653,7 +1650,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>2</v>
       </c>
@@ -1697,7 +1694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>3</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>3</v>
       </c>
@@ -1785,7 +1782,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>3</v>
       </c>
@@ -1829,7 +1826,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>3</v>
       </c>
@@ -1873,7 +1870,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>3</v>
       </c>
@@ -1917,7 +1914,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>3</v>
       </c>
@@ -1961,7 +1958,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>3</v>
       </c>
@@ -2005,7 +2002,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>3</v>
       </c>
@@ -2049,7 +2046,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>3</v>
       </c>
@@ -2093,7 +2090,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>3</v>
       </c>
@@ -2137,7 +2134,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>3</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>3</v>
       </c>
@@ -2225,7 +2222,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>3</v>
       </c>
@@ -2269,7 +2266,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>3</v>
       </c>
@@ -2313,7 +2310,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>3</v>
       </c>
@@ -2357,7 +2354,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>3</v>
       </c>
@@ -2401,7 +2398,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>3</v>
       </c>
@@ -2445,7 +2442,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>3</v>
       </c>
@@ -2489,7 +2486,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>3</v>
       </c>
@@ -2533,7 +2530,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>3</v>
       </c>
@@ -2577,7 +2574,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>3</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>3</v>
       </c>
@@ -2665,7 +2662,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>3</v>
       </c>
@@ -2709,7 +2706,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>3</v>
       </c>
@@ -2753,7 +2750,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>3</v>
       </c>
@@ -2797,7 +2794,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>3</v>
       </c>
@@ -2841,7 +2838,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>4</v>
       </c>
@@ -2885,7 +2882,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>4</v>
       </c>
@@ -2929,7 +2926,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>4</v>
       </c>
@@ -2973,7 +2970,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>4</v>
       </c>
@@ -3017,7 +3014,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>5</v>
       </c>
@@ -3031,7 +3028,7 @@
         <v>-88.3</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F49" s="6">
         <v>48.534031409999997</v>
@@ -3061,7 +3058,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>5</v>
       </c>
@@ -3075,7 +3072,7 @@
         <v>-45</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F50" s="6">
         <v>50.702341140000001</v>
@@ -3105,7 +3102,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>6</v>
       </c>
@@ -3149,7 +3146,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>6</v>
       </c>
@@ -3193,7 +3190,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>6</v>
       </c>
@@ -3237,7 +3234,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>6</v>
       </c>
@@ -3281,7 +3278,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>6</v>
       </c>
@@ -3325,7 +3322,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>6</v>
       </c>
@@ -3369,7 +3366,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>6</v>
       </c>
@@ -3413,7 +3410,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>6</v>
       </c>
@@ -3457,7 +3454,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>6</v>
       </c>
@@ -3501,7 +3498,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>6</v>
       </c>
@@ -3545,7 +3542,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>6</v>
       </c>
@@ -3589,7 +3586,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>6</v>
       </c>
@@ -3633,7 +3630,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>6</v>
       </c>
@@ -3677,7 +3674,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>6</v>
       </c>
@@ -3721,7 +3718,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>6</v>
       </c>
@@ -3765,7 +3762,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>6</v>
       </c>
@@ -3809,7 +3806,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>6</v>
       </c>
@@ -3853,7 +3850,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>6</v>
       </c>
@@ -3897,7 +3894,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>6</v>
       </c>
@@ -3941,7 +3938,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>6</v>
       </c>
@@ -3985,7 +3982,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>6</v>
       </c>
@@ -4029,7 +4026,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>6</v>
       </c>
@@ -4073,7 +4070,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>6</v>
       </c>
@@ -4117,7 +4114,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>6</v>
       </c>
@@ -4161,7 +4158,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>6</v>
       </c>
@@ -4205,7 +4202,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>6</v>
       </c>
@@ -4249,7 +4246,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>6</v>
       </c>
@@ -4293,7 +4290,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>6</v>
       </c>
@@ -4337,7 +4334,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>7</v>
       </c>
@@ -4381,7 +4378,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>7</v>
       </c>
@@ -4425,7 +4422,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>7</v>
       </c>
@@ -4469,7 +4466,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>7</v>
       </c>
@@ -4513,7 +4510,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>7</v>
       </c>
@@ -4557,7 +4554,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>7</v>
       </c>
@@ -4601,7 +4598,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>7</v>
       </c>
@@ -4645,7 +4642,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>7</v>
       </c>
@@ -4689,7 +4686,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>7</v>
       </c>
@@ -4733,7 +4730,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>8</v>
       </c>
@@ -4777,7 +4774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>8</v>
       </c>
@@ -4821,7 +4818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>8</v>
       </c>
@@ -4865,7 +4862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>8</v>
       </c>
@@ -4909,7 +4906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>8</v>
       </c>
@@ -4953,7 +4950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>8</v>
       </c>
@@ -4997,7 +4994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>8</v>
       </c>
@@ -5041,7 +5038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>8</v>
       </c>
@@ -5085,7 +5082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>8</v>
       </c>
@@ -5129,7 +5126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>8</v>
       </c>
@@ -5173,7 +5170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>8</v>
       </c>
@@ -5217,7 +5214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>8</v>
       </c>
@@ -5261,7 +5258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>8</v>
       </c>
@@ -5305,7 +5302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>8</v>
       </c>
@@ -5349,7 +5346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>8</v>
       </c>
@@ -5393,7 +5390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>8</v>
       </c>
@@ -5437,7 +5434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>8</v>
       </c>
@@ -5481,7 +5478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>8</v>
       </c>
@@ -5525,7 +5522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>8</v>
       </c>
@@ -5569,7 +5566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>8</v>
       </c>
@@ -5613,7 +5610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>8</v>
       </c>
@@ -5657,7 +5654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>8</v>
       </c>
@@ -5701,7 +5698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>8</v>
       </c>
@@ -5745,7 +5742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>8</v>
       </c>
@@ -5789,7 +5786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>8</v>
       </c>
@@ -5833,7 +5830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>8</v>
       </c>
@@ -5877,7 +5874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>8</v>
       </c>
@@ -5921,7 +5918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>8</v>
       </c>
@@ -5965,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>8</v>
       </c>
@@ -6009,7 +6006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>8</v>
       </c>
@@ -6053,7 +6050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>8</v>
       </c>
@@ -6097,7 +6094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>8</v>
       </c>
@@ -6141,7 +6138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>8</v>
       </c>
@@ -6185,7 +6182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>8</v>
       </c>
@@ -6229,7 +6226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>8</v>
       </c>
@@ -6273,7 +6270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>8</v>
       </c>
@@ -6317,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>8</v>
       </c>
@@ -6361,7 +6358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>8</v>
       </c>
@@ -6405,7 +6402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>8</v>
       </c>
@@ -6449,7 +6446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>8</v>
       </c>
@@ -6493,7 +6490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>8</v>
       </c>
@@ -6537,7 +6534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>8</v>
       </c>
@@ -6581,7 +6578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>8</v>
       </c>
@@ -6625,7 +6622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>8</v>
       </c>
@@ -6669,7 +6666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>8</v>
       </c>
@@ -6713,7 +6710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>8</v>
       </c>
@@ -6757,7 +6754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>8</v>
       </c>
@@ -6801,7 +6798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>8</v>
       </c>
@@ -6845,7 +6842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>8</v>
       </c>
@@ -6889,7 +6886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>8</v>
       </c>
@@ -6933,7 +6930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>8</v>
       </c>
@@ -6977,7 +6974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>8</v>
       </c>
@@ -7021,7 +7018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>8</v>
       </c>
@@ -7065,7 +7062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>8</v>
       </c>
@@ -7109,7 +7106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>8</v>
       </c>
@@ -7153,7 +7150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>8</v>
       </c>
@@ -7197,7 +7194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>8</v>
       </c>
@@ -7241,7 +7238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>8</v>
       </c>
@@ -7285,7 +7282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>8</v>
       </c>
@@ -7329,7 +7326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>8</v>
       </c>
@@ -7373,7 +7370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>8</v>
       </c>
@@ -7417,7 +7414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>8</v>
       </c>
@@ -7461,7 +7458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>8</v>
       </c>
@@ -7505,7 +7502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>8</v>
       </c>
@@ -7549,7 +7546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>8</v>
       </c>
@@ -7593,7 +7590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>8</v>
       </c>
@@ -7637,7 +7634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>8</v>
       </c>
@@ -7681,7 +7678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>8</v>
       </c>
@@ -7725,7 +7722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>8</v>
       </c>
@@ -7769,7 +7766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>8</v>
       </c>
@@ -7813,7 +7810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>8</v>
       </c>
@@ -7857,7 +7854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>8</v>
       </c>
@@ -7901,7 +7898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>9</v>
       </c>
@@ -7909,43 +7906,43 @@
         <v>22</v>
       </c>
       <c r="C160" s="6">
-        <v>44.25</v>
+        <v>24.53</v>
       </c>
       <c r="D160" s="6">
-        <v>-122.17</v>
+        <v>101.02</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F160" s="6">
-        <v>126.7379679</v>
+        <v>92.857142859999996</v>
       </c>
       <c r="G160" s="6">
-        <v>15.33</v>
+        <v>28.33</v>
       </c>
       <c r="H160" s="6">
-        <v>5.43</v>
-      </c>
-      <c r="I160" s="6" t="s">
-        <v>54</v>
+        <v>5.7</v>
+      </c>
+      <c r="I160" s="6">
+        <v>15.727272729999999</v>
       </c>
       <c r="J160" s="6">
-        <v>0.60743180900000004</v>
+        <v>2.5</v>
       </c>
       <c r="K160" s="9">
-        <v>50</v>
+        <v>2768</v>
       </c>
       <c r="L160" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M160" s="6">
-        <v>0.68530095000000002</v>
+        <v>0.83933827500000002</v>
       </c>
       <c r="N160" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>9</v>
       </c>
@@ -7953,43 +7950,43 @@
         <v>22</v>
       </c>
       <c r="C161" s="6">
-        <v>44.25</v>
+        <v>24.53</v>
       </c>
       <c r="D161" s="6">
-        <v>-122.17</v>
+        <v>101.02</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F161" s="6">
-        <v>126.7379679</v>
+        <v>92.857142859999996</v>
       </c>
       <c r="G161" s="6">
-        <v>15.33</v>
+        <v>28.33</v>
       </c>
       <c r="H161" s="6">
-        <v>5.43</v>
-      </c>
-      <c r="I161" s="6" t="s">
-        <v>54</v>
+        <v>5.7</v>
+      </c>
+      <c r="I161" s="6">
+        <v>15.727272729999999</v>
       </c>
       <c r="J161" s="6">
-        <v>0.60743180900000004</v>
+        <v>2.5</v>
       </c>
       <c r="K161" s="9">
-        <v>50</v>
+        <v>2768</v>
       </c>
       <c r="L161" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M161" s="6">
-        <v>0.66987812099999999</v>
+        <v>0.79367652899999996</v>
       </c>
       <c r="N161" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>9</v>
       </c>
@@ -7997,43 +7994,43 @@
         <v>22</v>
       </c>
       <c r="C162" s="6">
-        <v>44.25</v>
+        <v>24.53</v>
       </c>
       <c r="D162" s="6">
-        <v>-122.17</v>
+        <v>101.02</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F162" s="6">
-        <v>126.7379679</v>
+        <v>92.857142859999996</v>
       </c>
       <c r="G162" s="6">
-        <v>15.33</v>
+        <v>28.33</v>
       </c>
       <c r="H162" s="6">
-        <v>5.43</v>
-      </c>
-      <c r="I162" s="6" t="s">
-        <v>54</v>
+        <v>5.7</v>
+      </c>
+      <c r="I162" s="6">
+        <v>15.727272729999999</v>
       </c>
       <c r="J162" s="6">
-        <v>0.60743180900000004</v>
+        <v>2.5</v>
       </c>
       <c r="K162" s="9">
-        <v>50</v>
+        <v>2768</v>
       </c>
       <c r="L162" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M162" s="6">
-        <v>0.66037025100000002</v>
+        <v>0.76240596199999999</v>
       </c>
       <c r="N162" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>9</v>
       </c>
@@ -8041,219 +8038,219 @@
         <v>22</v>
       </c>
       <c r="C163" s="6">
-        <v>44.25</v>
+        <v>24.53</v>
       </c>
       <c r="D163" s="6">
-        <v>-122.17</v>
+        <v>101.02</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F163" s="6">
-        <v>126.7379679</v>
+        <v>92.857142859999996</v>
       </c>
       <c r="G163" s="6">
-        <v>15.33</v>
+        <v>28.33</v>
       </c>
       <c r="H163" s="6">
-        <v>5.43</v>
-      </c>
-      <c r="I163" s="6" t="s">
-        <v>54</v>
+        <v>5.7</v>
+      </c>
+      <c r="I163" s="6">
+        <v>15.727272729999999</v>
       </c>
       <c r="J163" s="6">
-        <v>0.60743180900000004</v>
+        <v>2.5</v>
       </c>
       <c r="K163" s="9">
-        <v>50</v>
+        <v>2768</v>
       </c>
       <c r="L163" s="3">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="M163" s="6">
-        <v>0.648487284</v>
+        <v>0.75275303699999996</v>
       </c>
       <c r="N163" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C164" s="6">
-        <v>24.53</v>
+        <v>21.9</v>
       </c>
       <c r="D164" s="6">
-        <v>101.02</v>
+        <v>101.27</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F164" s="6">
-        <v>92.857142859999996</v>
+        <v>46.835443040000001</v>
       </c>
       <c r="G164" s="6">
-        <v>28.33</v>
+        <v>34.67</v>
       </c>
       <c r="H164" s="6">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="I164" s="6">
-        <v>15.727272729999999</v>
+        <v>9.9285714289999998</v>
       </c>
       <c r="J164" s="6">
-        <v>2.5</v>
+        <v>0.52</v>
       </c>
       <c r="K164" s="9">
-        <v>2768</v>
+        <v>556</v>
       </c>
       <c r="L164" s="3">
         <v>7</v>
       </c>
       <c r="M164" s="6">
-        <v>0.83933827500000002</v>
+        <v>0.79539658999999996</v>
       </c>
       <c r="N164" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C165" s="6">
-        <v>24.53</v>
+        <v>21.9</v>
       </c>
       <c r="D165" s="6">
-        <v>101.02</v>
+        <v>101.27</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F165" s="6">
-        <v>92.857142859999996</v>
+        <v>46.835443040000001</v>
       </c>
       <c r="G165" s="6">
-        <v>28.33</v>
+        <v>34.67</v>
       </c>
       <c r="H165" s="6">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="I165" s="6">
-        <v>15.727272729999999</v>
+        <v>9.9285714289999998</v>
       </c>
       <c r="J165" s="6">
-        <v>2.5</v>
+        <v>0.52</v>
       </c>
       <c r="K165" s="9">
-        <v>2768</v>
+        <v>556</v>
       </c>
       <c r="L165" s="3">
         <v>14</v>
       </c>
       <c r="M165" s="6">
-        <v>0.79367652899999996</v>
+        <v>0.76893484400000001</v>
       </c>
       <c r="N165" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C166" s="6">
-        <v>24.53</v>
+        <v>21.9</v>
       </c>
       <c r="D166" s="6">
-        <v>101.02</v>
+        <v>101.27</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F166" s="6">
-        <v>92.857142859999996</v>
+        <v>46.835443040000001</v>
       </c>
       <c r="G166" s="6">
-        <v>28.33</v>
+        <v>34.67</v>
       </c>
       <c r="H166" s="6">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="I166" s="6">
-        <v>15.727272729999999</v>
+        <v>9.9285714289999998</v>
       </c>
       <c r="J166" s="6">
-        <v>2.5</v>
+        <v>0.52</v>
       </c>
       <c r="K166" s="9">
-        <v>2768</v>
+        <v>556</v>
       </c>
       <c r="L166" s="3">
         <v>21</v>
       </c>
       <c r="M166" s="6">
-        <v>0.76240596199999999</v>
+        <v>0.75926427799999996</v>
       </c>
       <c r="N166" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C167" s="6">
-        <v>24.53</v>
+        <v>21.9</v>
       </c>
       <c r="D167" s="6">
-        <v>101.02</v>
+        <v>101.27</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F167" s="6">
-        <v>92.857142859999996</v>
+        <v>46.835443040000001</v>
       </c>
       <c r="G167" s="6">
-        <v>28.33</v>
+        <v>34.67</v>
       </c>
       <c r="H167" s="6">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="I167" s="6">
-        <v>15.727272729999999</v>
+        <v>9.9285714289999998</v>
       </c>
       <c r="J167" s="6">
-        <v>2.5</v>
+        <v>0.52</v>
       </c>
       <c r="K167" s="9">
-        <v>2768</v>
+        <v>556</v>
       </c>
       <c r="L167" s="3">
         <v>28</v>
       </c>
       <c r="M167" s="6">
-        <v>0.75275303699999996</v>
+        <v>0.75681135300000002</v>
       </c>
       <c r="N167" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>10</v>
       </c>
@@ -8261,43 +8258,43 @@
         <v>23</v>
       </c>
       <c r="C168" s="6">
-        <v>21.9</v>
+        <v>52.126455999999997</v>
       </c>
       <c r="D168" s="6">
-        <v>101.27</v>
+        <v>-106.613868</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F168" s="6">
-        <v>46.835443040000001</v>
+        <v>29.915966390000001</v>
       </c>
       <c r="G168" s="6">
-        <v>34.67</v>
+        <v>50.5</v>
       </c>
       <c r="H168" s="6">
-        <v>5.82</v>
+        <v>8.24</v>
       </c>
       <c r="I168" s="6">
-        <v>9.9285714289999998</v>
+        <v>11.072664359999999</v>
       </c>
       <c r="J168" s="6">
-        <v>0.52</v>
+        <v>0.43732791799999998</v>
       </c>
       <c r="K168" s="9">
-        <v>556</v>
+        <v>100</v>
       </c>
       <c r="L168" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M168" s="6">
-        <v>0.79539658999999996</v>
+        <v>0.772000405</v>
       </c>
       <c r="N168" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>10</v>
       </c>
@@ -8305,43 +8302,43 @@
         <v>23</v>
       </c>
       <c r="C169" s="6">
-        <v>21.9</v>
+        <v>52.126455999999997</v>
       </c>
       <c r="D169" s="6">
-        <v>101.27</v>
+        <v>-106.613868</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F169" s="6">
-        <v>46.835443040000001</v>
+        <v>29.915966390000001</v>
       </c>
       <c r="G169" s="6">
-        <v>34.67</v>
+        <v>50.5</v>
       </c>
       <c r="H169" s="6">
-        <v>5.82</v>
+        <v>8.24</v>
       </c>
       <c r="I169" s="6">
-        <v>9.9285714289999998</v>
+        <v>11.072664359999999</v>
       </c>
       <c r="J169" s="6">
-        <v>0.52</v>
+        <v>0.43732791799999998</v>
       </c>
       <c r="K169" s="9">
-        <v>556</v>
+        <v>100</v>
       </c>
       <c r="L169" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M169" s="6">
-        <v>0.76893484400000001</v>
+        <v>0.74572715599999995</v>
       </c>
       <c r="N169" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>10</v>
       </c>
@@ -8349,43 +8346,43 @@
         <v>23</v>
       </c>
       <c r="C170" s="6">
-        <v>21.9</v>
+        <v>52.126455999999997</v>
       </c>
       <c r="D170" s="6">
-        <v>101.27</v>
+        <v>-106.613868</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F170" s="6">
-        <v>46.835443040000001</v>
+        <v>29.915966390000001</v>
       </c>
       <c r="G170" s="6">
-        <v>34.67</v>
+        <v>50.5</v>
       </c>
       <c r="H170" s="6">
-        <v>5.82</v>
+        <v>8.24</v>
       </c>
       <c r="I170" s="6">
-        <v>9.9285714289999998</v>
+        <v>11.072664359999999</v>
       </c>
       <c r="J170" s="6">
-        <v>0.52</v>
+        <v>0.43732791799999998</v>
       </c>
       <c r="K170" s="9">
-        <v>556</v>
+        <v>100</v>
       </c>
       <c r="L170" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M170" s="6">
-        <v>0.75926427799999996</v>
+        <v>0.73068572700000001</v>
       </c>
       <c r="N170" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>10</v>
       </c>
@@ -8393,48 +8390,48 @@
         <v>23</v>
       </c>
       <c r="C171" s="6">
-        <v>21.9</v>
+        <v>52.126455999999997</v>
       </c>
       <c r="D171" s="6">
-        <v>101.27</v>
+        <v>-106.613868</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F171" s="6">
-        <v>46.835443040000001</v>
+        <v>29.915966390000001</v>
       </c>
       <c r="G171" s="6">
-        <v>34.67</v>
+        <v>50.5</v>
       </c>
       <c r="H171" s="6">
-        <v>5.82</v>
+        <v>8.24</v>
       </c>
       <c r="I171" s="6">
-        <v>9.9285714289999998</v>
+        <v>11.072664359999999</v>
       </c>
       <c r="J171" s="6">
-        <v>0.52</v>
+        <v>0.43732791799999998</v>
       </c>
       <c r="K171" s="9">
-        <v>556</v>
+        <v>100</v>
       </c>
       <c r="L171" s="3">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="M171" s="6">
-        <v>0.75681135300000002</v>
+        <v>0.70619415399999996</v>
       </c>
       <c r="N171" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C172" s="6">
         <v>52.126455999999997</v>
@@ -8464,21 +8461,21 @@
         <v>100</v>
       </c>
       <c r="L172" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M172" s="6">
-        <v>0.772000405</v>
+        <v>0.68725757499999995</v>
       </c>
       <c r="N172" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C173" s="6">
         <v>52.126455999999997</v>
@@ -8508,21 +8505,21 @@
         <v>100</v>
       </c>
       <c r="L173" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M173" s="6">
-        <v>0.74572715599999995</v>
+        <v>0.67209690700000002</v>
       </c>
       <c r="N173" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C174" s="6">
         <v>52.126455999999997</v>
@@ -8537,36 +8534,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G174" s="6">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="H174" s="6">
-        <v>8.24</v>
+        <v>7.71</v>
       </c>
       <c r="I174" s="6">
-        <v>11.072664359999999</v>
+        <v>14.28571429</v>
       </c>
       <c r="J174" s="6">
-        <v>0.43732791799999998</v>
+        <v>0.50746654599999996</v>
       </c>
       <c r="K174" s="9">
         <v>100</v>
       </c>
       <c r="L174" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M174" s="6">
-        <v>0.73068572700000001</v>
+        <v>0.66152867900000001</v>
       </c>
       <c r="N174" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C175" s="6">
         <v>52.126455999999997</v>
@@ -8581,36 +8578,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G175" s="6">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="H175" s="6">
-        <v>8.24</v>
+        <v>7.71</v>
       </c>
       <c r="I175" s="6">
-        <v>11.072664359999999</v>
+        <v>14.28571429</v>
       </c>
       <c r="J175" s="6">
-        <v>0.43732791799999998</v>
+        <v>0.50746654599999996</v>
       </c>
       <c r="K175" s="9">
         <v>100</v>
       </c>
       <c r="L175" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M175" s="6">
-        <v>0.70619415399999996</v>
+        <v>0.62589341799999998</v>
       </c>
       <c r="N175" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C176" s="6">
         <v>52.126455999999997</v>
@@ -8625,36 +8622,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G176" s="6">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="H176" s="6">
-        <v>8.24</v>
+        <v>7.71</v>
       </c>
       <c r="I176" s="6">
-        <v>11.072664359999999</v>
+        <v>14.28571429</v>
       </c>
       <c r="J176" s="6">
-        <v>0.43732791799999998</v>
+        <v>0.50746654599999996</v>
       </c>
       <c r="K176" s="9">
         <v>100</v>
       </c>
       <c r="L176" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M176" s="6">
-        <v>0.68725757499999995</v>
+        <v>0.60710718500000005</v>
       </c>
       <c r="N176" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C177" s="6">
         <v>52.126455999999997</v>
@@ -8669,36 +8666,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G177" s="6">
-        <v>50.5</v>
+        <v>46.3</v>
       </c>
       <c r="H177" s="6">
-        <v>8.24</v>
+        <v>7.71</v>
       </c>
       <c r="I177" s="6">
-        <v>11.072664359999999</v>
+        <v>14.28571429</v>
       </c>
       <c r="J177" s="6">
-        <v>0.43732791799999998</v>
+        <v>0.50746654599999996</v>
       </c>
       <c r="K177" s="9">
         <v>100</v>
       </c>
       <c r="L177" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M177" s="6">
-        <v>0.67209690700000002</v>
+        <v>0.57512600400000002</v>
       </c>
       <c r="N177" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C178" s="6">
         <v>52.126455999999997</v>
@@ -8728,21 +8725,21 @@
         <v>100</v>
       </c>
       <c r="L178" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M178" s="6">
-        <v>0.66152867900000001</v>
+        <v>0.55057221899999997</v>
       </c>
       <c r="N178" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C179" s="6">
         <v>52.126455999999997</v>
@@ -8772,21 +8769,21 @@
         <v>100</v>
       </c>
       <c r="L179" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M179" s="6">
-        <v>0.62589341799999998</v>
+        <v>0.52979434400000003</v>
       </c>
       <c r="N179" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C180" s="6">
         <v>52.126455999999997</v>
@@ -8801,36 +8798,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G180" s="6">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="H180" s="6">
-        <v>7.71</v>
+        <v>8.14</v>
       </c>
       <c r="I180" s="6">
-        <v>14.28571429</v>
+        <v>11.80555556</v>
       </c>
       <c r="J180" s="6">
-        <v>0.50746654599999996</v>
+        <v>0.45536335</v>
       </c>
       <c r="K180" s="9">
         <v>100</v>
       </c>
       <c r="L180" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M180" s="6">
-        <v>0.60710718500000005</v>
+        <v>0.73829716700000003</v>
       </c>
       <c r="N180" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C181" s="6">
         <v>52.126455999999997</v>
@@ -8845,36 +8842,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G181" s="6">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="H181" s="6">
-        <v>7.71</v>
+        <v>8.14</v>
       </c>
       <c r="I181" s="6">
-        <v>14.28571429</v>
+        <v>11.80555556</v>
       </c>
       <c r="J181" s="6">
-        <v>0.50746654599999996</v>
+        <v>0.45536335</v>
       </c>
       <c r="K181" s="9">
         <v>100</v>
       </c>
       <c r="L181" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M181" s="6">
-        <v>0.57512600400000002</v>
+        <v>0.69329989599999997</v>
       </c>
       <c r="N181" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C182" s="6">
         <v>52.126455999999997</v>
@@ -8889,36 +8886,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G182" s="6">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="H182" s="6">
-        <v>7.71</v>
+        <v>8.14</v>
       </c>
       <c r="I182" s="6">
-        <v>14.28571429</v>
+        <v>11.80555556</v>
       </c>
       <c r="J182" s="6">
-        <v>0.50746654599999996</v>
+        <v>0.45536335</v>
       </c>
       <c r="K182" s="9">
         <v>100</v>
       </c>
       <c r="L182" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M182" s="6">
-        <v>0.55057221899999997</v>
+        <v>0.66702405399999998</v>
       </c>
       <c r="N182" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C183" s="6">
         <v>52.126455999999997</v>
@@ -8933,36 +8930,36 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G183" s="6">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="H183" s="6">
-        <v>7.71</v>
+        <v>8.14</v>
       </c>
       <c r="I183" s="6">
-        <v>14.28571429</v>
+        <v>11.80555556</v>
       </c>
       <c r="J183" s="6">
-        <v>0.50746654599999996</v>
+        <v>0.45536335</v>
       </c>
       <c r="K183" s="9">
         <v>100</v>
       </c>
       <c r="L183" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M183" s="6">
-        <v>0.52979434400000003</v>
+        <v>0.62380845900000004</v>
       </c>
       <c r="N183" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C184" s="6">
         <v>52.126455999999997</v>
@@ -8992,21 +8989,21 @@
         <v>100</v>
       </c>
       <c r="L184" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M184" s="6">
-        <v>0.73829716700000003</v>
+        <v>0.58802026200000002</v>
       </c>
       <c r="N184" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C185" s="6">
         <v>52.126455999999997</v>
@@ -9036,21 +9033,21 @@
         <v>100</v>
       </c>
       <c r="L185" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M185" s="6">
-        <v>0.69329989599999997</v>
+        <v>0.55975537099999995</v>
       </c>
       <c r="N185" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C186" s="6">
         <v>52.126455999999997</v>
@@ -9065,13 +9062,13 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G186" s="6">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="H186" s="6">
-        <v>8.14</v>
+        <v>7.88</v>
       </c>
       <c r="I186" s="6">
-        <v>11.80555556</v>
+        <v>9.7701149429999994</v>
       </c>
       <c r="J186" s="6">
         <v>0.45536335</v>
@@ -9080,21 +9077,21 @@
         <v>100</v>
       </c>
       <c r="L186" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M186" s="6">
-        <v>0.66702405399999998</v>
+        <v>0.62408063599999997</v>
       </c>
       <c r="N186" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C187" s="6">
         <v>52.126455999999997</v>
@@ -9109,13 +9106,13 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G187" s="6">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="H187" s="6">
-        <v>8.14</v>
+        <v>7.88</v>
       </c>
       <c r="I187" s="6">
-        <v>11.80555556</v>
+        <v>9.7701149429999994</v>
       </c>
       <c r="J187" s="6">
         <v>0.45536335</v>
@@ -9124,21 +9121,21 @@
         <v>100</v>
       </c>
       <c r="L187" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M187" s="6">
-        <v>0.62380845900000004</v>
+        <v>0.58095576699999996</v>
       </c>
       <c r="N187" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C188" s="6">
         <v>52.126455999999997</v>
@@ -9153,13 +9150,13 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G188" s="6">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="H188" s="6">
-        <v>8.14</v>
+        <v>7.88</v>
       </c>
       <c r="I188" s="6">
-        <v>11.80555556</v>
+        <v>9.7701149429999994</v>
       </c>
       <c r="J188" s="6">
         <v>0.45536335</v>
@@ -9168,21 +9165,21 @@
         <v>100</v>
       </c>
       <c r="L188" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M188" s="6">
-        <v>0.58802026200000002</v>
+        <v>0.558427322</v>
       </c>
       <c r="N188" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C189" s="6">
         <v>52.126455999999997</v>
@@ -9197,13 +9194,13 @@
         <v>29.915966390000001</v>
       </c>
       <c r="G189" s="6">
-        <v>45.9</v>
+        <v>41</v>
       </c>
       <c r="H189" s="6">
-        <v>8.14</v>
+        <v>7.88</v>
       </c>
       <c r="I189" s="6">
-        <v>11.80555556</v>
+        <v>9.7701149429999994</v>
       </c>
       <c r="J189" s="6">
         <v>0.45536335</v>
@@ -9212,21 +9209,21 @@
         <v>100</v>
       </c>
       <c r="L189" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M189" s="6">
-        <v>0.55975537099999995</v>
+        <v>0.51895393899999998</v>
       </c>
       <c r="N189" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C190" s="6">
         <v>52.126455999999997</v>
@@ -9256,21 +9253,21 @@
         <v>100</v>
       </c>
       <c r="L190" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M190" s="6">
-        <v>0.62408063599999997</v>
+        <v>0.486910546</v>
       </c>
       <c r="N190" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C191" s="6">
         <v>52.126455999999997</v>
@@ -9300,16 +9297,16 @@
         <v>100</v>
       </c>
       <c r="L191" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M191" s="6">
-        <v>0.58095576699999996</v>
+        <v>0.46238786700000001</v>
       </c>
       <c r="N191" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>11</v>
       </c>
@@ -9317,43 +9314,43 @@
         <v>24</v>
       </c>
       <c r="C192" s="6">
-        <v>52.126455999999997</v>
+        <v>26.32</v>
       </c>
       <c r="D192" s="6">
-        <v>-106.613868</v>
+        <v>117.6</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F192" s="6">
-        <v>29.915966390000001</v>
+        <v>55.481727569999997</v>
       </c>
       <c r="G192" s="6">
-        <v>41</v>
+        <v>13.5</v>
       </c>
       <c r="H192" s="6">
-        <v>7.88</v>
+        <v>5.2</v>
       </c>
       <c r="I192" s="6">
-        <v>9.7701149429999994</v>
+        <v>13.5</v>
       </c>
       <c r="J192" s="6">
-        <v>0.45536335</v>
+        <v>0.36980000000000002</v>
       </c>
       <c r="K192" s="9">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L192" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M192" s="6">
-        <v>0.558427322</v>
+        <v>0.76435185000000005</v>
       </c>
       <c r="N192" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>11</v>
       </c>
@@ -9361,43 +9358,43 @@
         <v>24</v>
       </c>
       <c r="C193" s="6">
-        <v>52.126455999999997</v>
+        <v>26.32</v>
       </c>
       <c r="D193" s="6">
-        <v>-106.613868</v>
+        <v>117.6</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F193" s="6">
-        <v>29.915966390000001</v>
+        <v>55.481727569999997</v>
       </c>
       <c r="G193" s="6">
-        <v>41</v>
+        <v>13.5</v>
       </c>
       <c r="H193" s="6">
-        <v>7.88</v>
+        <v>5.2</v>
       </c>
       <c r="I193" s="6">
-        <v>9.7701149429999994</v>
+        <v>13.5</v>
       </c>
       <c r="J193" s="6">
-        <v>0.45536335</v>
+        <v>0.36980000000000002</v>
       </c>
       <c r="K193" s="9">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L193" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M193" s="6">
-        <v>0.51895393899999998</v>
+        <v>0.75983797500000005</v>
       </c>
       <c r="N193" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>11</v>
       </c>
@@ -9405,43 +9402,43 @@
         <v>24</v>
       </c>
       <c r="C194" s="6">
-        <v>52.126455999999997</v>
+        <v>26.32</v>
       </c>
       <c r="D194" s="6">
-        <v>-106.613868</v>
+        <v>117.6</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F194" s="6">
-        <v>29.915966390000001</v>
+        <v>55.481727569999997</v>
       </c>
       <c r="G194" s="6">
-        <v>41</v>
+        <v>13.5</v>
       </c>
       <c r="H194" s="6">
-        <v>7.88</v>
+        <v>5.2</v>
       </c>
       <c r="I194" s="6">
-        <v>9.7701149429999994</v>
+        <v>13.5</v>
       </c>
       <c r="J194" s="6">
-        <v>0.45536335</v>
+        <v>0.36980000000000002</v>
       </c>
       <c r="K194" s="9">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L194" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M194" s="6">
-        <v>0.486910546</v>
+        <v>0.74444445000000004</v>
       </c>
       <c r="N194" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>11</v>
       </c>
@@ -9449,48 +9446,48 @@
         <v>24</v>
       </c>
       <c r="C195" s="6">
-        <v>52.126455999999997</v>
+        <v>26.32</v>
       </c>
       <c r="D195" s="6">
-        <v>-106.613868</v>
+        <v>117.6</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F195" s="6">
-        <v>29.915966390000001</v>
+        <v>55.481727569999997</v>
       </c>
       <c r="G195" s="6">
-        <v>41</v>
+        <v>13.5</v>
       </c>
       <c r="H195" s="6">
-        <v>7.88</v>
+        <v>5.2</v>
       </c>
       <c r="I195" s="6">
-        <v>9.7701149429999994</v>
+        <v>13.5</v>
       </c>
       <c r="J195" s="6">
-        <v>0.45536335</v>
+        <v>0.36980000000000002</v>
       </c>
       <c r="K195" s="9">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L195" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="M195" s="6">
-        <v>0.46238786700000001</v>
+        <v>0.72685184999999997</v>
       </c>
       <c r="N195" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C196" s="6">
         <v>26.32</v>
@@ -9520,21 +9517,21 @@
         <v>400</v>
       </c>
       <c r="L196" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M196" s="6">
-        <v>0.76435185000000005</v>
+        <v>0.70648147500000003</v>
       </c>
       <c r="N196" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C197" s="6">
         <v>26.32</v>
@@ -9549,36 +9546,36 @@
         <v>55.481727569999997</v>
       </c>
       <c r="G197" s="6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="H197" s="6">
         <v>5.2</v>
       </c>
       <c r="I197" s="6">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="J197" s="6">
-        <v>0.36980000000000002</v>
+        <v>0.31269999999999998</v>
       </c>
       <c r="K197" s="9">
         <v>400</v>
       </c>
       <c r="L197" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M197" s="6">
-        <v>0.75983797500000005</v>
+        <v>0.80243055600000002</v>
       </c>
       <c r="N197" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C198" s="6">
         <v>26.32</v>
@@ -9593,36 +9590,36 @@
         <v>55.481727569999997</v>
       </c>
       <c r="G198" s="6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="H198" s="6">
         <v>5.2</v>
       </c>
       <c r="I198" s="6">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="J198" s="6">
-        <v>0.36980000000000002</v>
+        <v>0.31269999999999998</v>
       </c>
       <c r="K198" s="9">
         <v>400</v>
       </c>
       <c r="L198" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M198" s="6">
-        <v>0.74444445000000004</v>
+        <v>0.798148148</v>
       </c>
       <c r="N198" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C199" s="6">
         <v>26.32</v>
@@ -9637,36 +9634,36 @@
         <v>55.481727569999997</v>
       </c>
       <c r="G199" s="6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="H199" s="6">
         <v>5.2</v>
       </c>
       <c r="I199" s="6">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="J199" s="6">
-        <v>0.36980000000000002</v>
+        <v>0.31269999999999998</v>
       </c>
       <c r="K199" s="9">
         <v>400</v>
       </c>
       <c r="L199" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M199" s="6">
-        <v>0.72685184999999997</v>
+        <v>0.78425925900000004</v>
       </c>
       <c r="N199" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C200" s="6">
         <v>26.32</v>
@@ -9681,36 +9678,36 @@
         <v>55.481727569999997</v>
       </c>
       <c r="G200" s="6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="H200" s="6">
         <v>5.2</v>
       </c>
       <c r="I200" s="6">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="J200" s="6">
-        <v>0.36980000000000002</v>
+        <v>0.31269999999999998</v>
       </c>
       <c r="K200" s="9">
         <v>400</v>
       </c>
       <c r="L200" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M200" s="6">
-        <v>0.70648147500000003</v>
+        <v>0.76319444400000003</v>
       </c>
       <c r="N200" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C201" s="6">
         <v>26.32</v>
@@ -9740,16 +9737,16 @@
         <v>400</v>
       </c>
       <c r="L201" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M201" s="6">
-        <v>0.80243055600000002</v>
+        <v>0.75023148100000003</v>
       </c>
       <c r="N201" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>12</v>
       </c>
@@ -9757,43 +9754,43 @@
         <v>25</v>
       </c>
       <c r="C202" s="6">
-        <v>26.32</v>
+        <v>19.414200000000001</v>
       </c>
       <c r="D202" s="6">
-        <v>117.6</v>
+        <v>-155.23400000000001</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F202" s="6">
-        <v>55.481727569999997</v>
+        <v>96.153846150000007</v>
       </c>
       <c r="G202" s="6">
-        <v>16.5</v>
+        <v>2</v>
       </c>
       <c r="H202" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="I202" s="6">
-        <v>14.7</v>
+        <v>5.26</v>
+      </c>
+      <c r="I202" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="J202" s="6">
-        <v>0.31269999999999998</v>
+        <v>1.0274340310000001</v>
       </c>
       <c r="K202" s="9">
-        <v>400</v>
+        <v>946.66666699999996</v>
       </c>
       <c r="L202" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M202" s="6">
-        <v>0.798148148</v>
+        <v>0.43930000000000002</v>
       </c>
       <c r="N202" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>12</v>
       </c>
@@ -9801,43 +9798,43 @@
         <v>25</v>
       </c>
       <c r="C203" s="6">
-        <v>26.32</v>
+        <v>19.928599999999999</v>
       </c>
       <c r="D203" s="6">
-        <v>117.6</v>
+        <v>-155.30099999999999</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F203" s="6">
-        <v>55.481727569999997</v>
-      </c>
-      <c r="G203" s="6">
-        <v>16.5</v>
+        <v>96.153846150000007</v>
+      </c>
+      <c r="G203" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="H203" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="I203" s="6">
-        <v>14.7</v>
+        <v>3.9</v>
+      </c>
+      <c r="I203" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="J203" s="6">
-        <v>0.31269999999999998</v>
+        <v>1.034573596</v>
       </c>
       <c r="K203" s="9">
-        <v>400</v>
+        <v>946.66666699999996</v>
       </c>
       <c r="L203" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M203" s="6">
-        <v>0.78425925900000004</v>
+        <v>0.41720000000000002</v>
       </c>
       <c r="N203" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>12</v>
       </c>
@@ -9845,215 +9842,39 @@
         <v>25</v>
       </c>
       <c r="C204" s="6">
-        <v>26.32</v>
+        <v>20.051100000000002</v>
       </c>
       <c r="D204" s="6">
-        <v>117.6</v>
+        <v>-115.684</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F204" s="6">
-        <v>55.481727569999997</v>
+        <v>96.153846150000007</v>
       </c>
       <c r="G204" s="6">
-        <v>16.5</v>
+        <v>43</v>
       </c>
       <c r="H204" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="I204" s="6">
-        <v>14.7</v>
-      </c>
-      <c r="J204" s="6">
-        <v>0.31269999999999998</v>
+        <v>4.41</v>
+      </c>
+      <c r="I204" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J204" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="K204" s="9">
-        <v>400</v>
+        <v>946.66666699999996</v>
       </c>
       <c r="L204" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M204" s="6">
-        <v>0.76319444400000003</v>
+        <v>0.43290000000000001</v>
       </c>
       <c r="N204" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="3">
-        <v>12</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C205" s="6">
-        <v>26.32</v>
-      </c>
-      <c r="D205" s="6">
-        <v>117.6</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F205" s="6">
-        <v>55.481727569999997</v>
-      </c>
-      <c r="G205" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="H205" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="I205" s="6">
-        <v>14.7</v>
-      </c>
-      <c r="J205" s="6">
-        <v>0.31269999999999998</v>
-      </c>
-      <c r="K205" s="9">
-        <v>400</v>
-      </c>
-      <c r="L205" s="3">
-        <v>23</v>
-      </c>
-      <c r="M205" s="6">
-        <v>0.75023148100000003</v>
-      </c>
-      <c r="N205" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="3">
-        <v>13</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C206" s="6">
-        <v>19.414200000000001</v>
-      </c>
-      <c r="D206" s="6">
-        <v>-155.23400000000001</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F206" s="6">
-        <v>96.153846150000007</v>
-      </c>
-      <c r="G206" s="6">
-        <v>2</v>
-      </c>
-      <c r="H206" s="6">
-        <v>5.26</v>
-      </c>
-      <c r="I206" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J206" s="6">
-        <v>1.0274340310000001</v>
-      </c>
-      <c r="K206" s="9">
-        <v>946.66666699999996</v>
-      </c>
-      <c r="L206" s="3">
-        <v>4</v>
-      </c>
-      <c r="M206" s="6">
-        <v>0.43930000000000002</v>
-      </c>
-      <c r="N206" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="3">
-        <v>13</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C207" s="6">
-        <v>19.928599999999999</v>
-      </c>
-      <c r="D207" s="6">
-        <v>-155.30099999999999</v>
-      </c>
-      <c r="E207" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F207" s="6">
-        <v>96.153846150000007</v>
-      </c>
-      <c r="G207" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H207" s="6">
-        <v>3.9</v>
-      </c>
-      <c r="I207" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J207" s="6">
-        <v>1.034573596</v>
-      </c>
-      <c r="K207" s="9">
-        <v>946.66666699999996</v>
-      </c>
-      <c r="L207" s="3">
-        <v>4</v>
-      </c>
-      <c r="M207" s="6">
-        <v>0.41720000000000002</v>
-      </c>
-      <c r="N207" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="3">
-        <v>13</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C208" s="6">
-        <v>20.051100000000002</v>
-      </c>
-      <c r="D208" s="6">
-        <v>-115.684</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F208" s="6">
-        <v>96.153846150000007</v>
-      </c>
-      <c r="G208" s="6">
-        <v>43</v>
-      </c>
-      <c r="H208" s="6">
-        <v>4.41</v>
-      </c>
-      <c r="I208" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J208" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="K208" s="9">
-        <v>946.66666699999996</v>
-      </c>
-      <c r="L208" s="3">
-        <v>4</v>
-      </c>
-      <c r="M208" s="6">
-        <v>0.43290000000000001</v>
-      </c>
-      <c r="N208" s="3">
         <v>1.5</v>
       </c>
     </row>
@@ -10065,19 +9886,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F238F5-6035-4E09-8303-55A8A0E9A5B8}">
-  <dimension ref="A1:N110"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N109"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="1"/>
-    <col min="3" max="4" width="8.88671875" style="7"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="10" width="8.88671875" style="7"/>
-    <col min="11" max="11" width="8.88671875" style="10"/>
-    <col min="12" max="13" width="8.88671875" style="7"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="2" width="8.9140625" style="1"/>
+    <col min="3" max="4" width="8.9140625" style="7"/>
+    <col min="5" max="5" width="8.9140625" style="1"/>
+    <col min="6" max="10" width="8.9140625" style="7"/>
+    <col min="11" max="11" width="8.9140625" style="10"/>
+    <col min="12" max="13" width="8.9140625" style="7"/>
+    <col min="14" max="16384" width="8.9140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -10094,7 +9915,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>5</v>
@@ -10103,7 +9924,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>7</v>
@@ -10115,18 +9936,18 @@
         <v>9</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="6">
         <v>42.359031700000003</v>
@@ -10141,7 +9962,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H2" s="6">
         <v>4.2</v>
@@ -10165,12 +9986,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6">
         <v>42.359031700000003</v>
@@ -10185,7 +10006,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H3" s="6">
         <v>4.2</v>
@@ -10209,12 +10030,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="6">
         <v>42.359031700000003</v>
@@ -10229,7 +10050,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4" s="6">
         <v>4.2</v>
@@ -10253,12 +10074,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6">
         <v>42.359031700000003</v>
@@ -10273,7 +10094,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H5" s="6">
         <v>4.2</v>
@@ -10297,12 +10118,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6">
         <v>42.359031700000003</v>
@@ -10317,7 +10138,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H6" s="6">
         <v>4.2</v>
@@ -10341,12 +10162,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6">
         <v>42.359031700000003</v>
@@ -10361,7 +10182,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H7" s="6">
         <v>4.2</v>
@@ -10385,12 +10206,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="6">
         <v>42.359031700000003</v>
@@ -10405,7 +10226,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H8" s="6">
         <v>4.2</v>
@@ -10429,12 +10250,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="6">
         <v>42.359031700000003</v>
@@ -10449,7 +10270,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="6">
         <v>4.2</v>
@@ -10473,12 +10294,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="6">
         <v>42.359031700000003</v>
@@ -10493,7 +10314,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="6">
         <v>4.2</v>
@@ -10517,12 +10338,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6">
         <v>42.359031700000003</v>
@@ -10537,7 +10358,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" s="6">
         <v>4.2</v>
@@ -10561,12 +10382,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="6">
         <v>42.359031700000003</v>
@@ -10581,7 +10402,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H12" s="6">
         <v>4.2</v>
@@ -10605,12 +10426,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="6">
         <v>42.359031700000003</v>
@@ -10625,7 +10446,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H13" s="6">
         <v>4.2</v>
@@ -10649,12 +10470,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6">
         <v>42.359031700000003</v>
@@ -10669,7 +10490,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="6">
         <v>4.2</v>
@@ -10693,12 +10514,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="6">
         <v>42.359031700000003</v>
@@ -10713,7 +10534,7 @@
         <v>57.193877550000003</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H15" s="6">
         <v>4.2</v>
@@ -10737,12 +10558,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="6">
         <v>42.02</v>
@@ -10781,12 +10602,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>3</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="6">
         <v>42.748899999999999</v>
@@ -10801,13 +10622,13 @@
         <v>43.314917129999998</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J17" s="6">
         <v>0.1555506666</v>
@@ -10825,12 +10646,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>3</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="6">
         <v>42.748899999999999</v>
@@ -10845,13 +10666,13 @@
         <v>43.314917129999998</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J18" s="6">
         <v>0.18168135330000001</v>
@@ -10869,12 +10690,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="6">
         <v>56.45</v>
@@ -10883,7 +10704,7 @@
         <v>-3.0666669999999998</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="6">
         <v>39.344262299999997</v>
@@ -10913,12 +10734,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>4</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="6">
         <v>56.45</v>
@@ -10927,7 +10748,7 @@
         <v>-3.0666669999999998</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="6">
         <v>39.344262299999997</v>
@@ -10957,12 +10778,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>5</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="6">
         <v>52.270319999999998</v>
@@ -10977,7 +10798,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H21" s="6">
         <v>6.7</v>
@@ -11001,12 +10822,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>5</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="6">
         <v>52.270319999999998</v>
@@ -11021,7 +10842,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H22" s="6">
         <v>6.7</v>
@@ -11045,12 +10866,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>5</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="6">
         <v>52.270319999999998</v>
@@ -11065,7 +10886,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H23" s="6">
         <v>6.7</v>
@@ -11089,12 +10910,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="6">
         <v>52.270319999999998</v>
@@ -11109,7 +10930,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H24" s="6">
         <v>6.7</v>
@@ -11133,12 +10954,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>5</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="6">
         <v>52.270319999999998</v>
@@ -11153,7 +10974,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H25" s="6">
         <v>6.7</v>
@@ -11177,12 +10998,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="6">
         <v>52.270319999999998</v>
@@ -11197,7 +11018,7 @@
         <v>32.9787234</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H26" s="6">
         <v>6.7</v>
@@ -11221,12 +11042,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>6</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="6">
         <v>41.251111000000002</v>
@@ -11247,7 +11068,7 @@
         <v>6.8000001909999996</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J27" s="6">
         <v>0.49457210359999998</v>
@@ -11265,12 +11086,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="6">
         <v>41.251111000000002</v>
@@ -11291,7 +11112,7 @@
         <v>6.8000001909999996</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J28" s="6">
         <v>0.49457210359999998</v>
@@ -11309,12 +11130,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="6">
         <v>35.966667000000001</v>
@@ -11335,7 +11156,7 @@
         <v>5.3000001909999996</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J29" s="6">
         <v>0.25118283159999999</v>
@@ -11353,12 +11174,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="6">
         <v>51.541280999999998</v>
@@ -11397,12 +11218,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" s="6">
         <v>51.904167000000001</v>
@@ -11417,7 +11238,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H31" s="6">
         <v>7.6</v>
@@ -11441,12 +11262,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>8</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" s="6">
         <v>51.904167000000001</v>
@@ -11461,7 +11282,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="6">
         <v>7.6</v>
@@ -11485,12 +11306,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>8</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" s="6">
         <v>51.541280999999998</v>
@@ -11529,12 +11350,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6">
         <v>51.904167000000001</v>
@@ -11549,7 +11370,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H34" s="6">
         <v>7.6</v>
@@ -11573,12 +11394,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>8</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" s="6">
         <v>51.904167000000001</v>
@@ -11593,7 +11414,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H35" s="6">
         <v>7.6</v>
@@ -11617,12 +11438,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="6">
         <v>51.541280999999998</v>
@@ -11661,12 +11482,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>8</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="6">
         <v>51.904167000000001</v>
@@ -11681,7 +11502,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H37" s="6">
         <v>7.6</v>
@@ -11705,12 +11526,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>8</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="6">
         <v>51.904167000000001</v>
@@ -11725,7 +11546,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H38" s="6">
         <v>7.6</v>
@@ -11749,12 +11570,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>8</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="6">
         <v>51.541280999999998</v>
@@ -11793,12 +11614,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>8</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="6">
         <v>51.904167000000001</v>
@@ -11813,7 +11634,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H40" s="6">
         <v>7.6</v>
@@ -11837,12 +11658,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>8</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="6">
         <v>51.904167000000001</v>
@@ -11857,7 +11678,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H41" s="6">
         <v>7.6</v>
@@ -11881,12 +11702,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>8</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C42" s="6">
         <v>51.541280999999998</v>
@@ -11925,12 +11746,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>8</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C43" s="6">
         <v>51.904167000000001</v>
@@ -11945,7 +11766,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H43" s="6">
         <v>7.6</v>
@@ -11969,12 +11790,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" s="6">
         <v>51.904167000000001</v>
@@ -11989,7 +11810,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H44" s="6">
         <v>7.6</v>
@@ -12013,12 +11834,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45" s="6">
         <v>51.541280999999998</v>
@@ -12057,12 +11878,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>8</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C46" s="6">
         <v>51.904167000000001</v>
@@ -12077,7 +11898,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H46" s="6">
         <v>7.6</v>
@@ -12101,12 +11922,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>8</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47" s="6">
         <v>51.904167000000001</v>
@@ -12121,7 +11942,7 @@
         <v>48.742857139999998</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H47" s="6">
         <v>7.6</v>
@@ -12145,12 +11966,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>9</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="6">
         <v>37.616667</v>
@@ -12189,12 +12010,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>9</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="6">
         <v>37.616667</v>
@@ -12233,12 +12054,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>9</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="6">
         <v>37.616667</v>
@@ -12277,12 +12098,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>9</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="6">
         <v>37.616667</v>
@@ -12321,12 +12142,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>10</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C52" s="6">
         <v>-40.622245499999998</v>
@@ -12341,13 +12162,13 @@
         <v>43.632478630000001</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H52" s="6">
         <v>5.8</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J52" s="6">
         <v>0.69099999999999995</v>
@@ -12359,18 +12180,18 @@
         <v>3</v>
       </c>
       <c r="M52" s="6">
-        <v>0.65798867299999997</v>
+        <v>0.48039902699999998</v>
       </c>
       <c r="N52" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>10</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C53" s="6">
         <v>-40.622245499999998</v>
@@ -12385,13 +12206,13 @@
         <v>43.632478630000001</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H53" s="6">
         <v>5.8</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J53" s="6">
         <v>0.441</v>
@@ -12403,18 +12224,18 @@
         <v>3</v>
       </c>
       <c r="M53" s="6">
-        <v>0.50610155999999995</v>
+        <v>0.38892398500000003</v>
       </c>
       <c r="N53" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>10</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="6">
         <v>-40.622245499999998</v>
@@ -12429,13 +12250,13 @@
         <v>43.632478630000001</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H54" s="6">
         <v>5.7</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J54" s="6">
         <v>1.038</v>
@@ -12447,18 +12268,18 @@
         <v>3</v>
       </c>
       <c r="M54" s="6">
-        <v>0.50324036500000002</v>
+        <v>0.50268226800000004</v>
       </c>
       <c r="N54" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55" s="6">
         <v>-40.622245499999998</v>
@@ -12473,13 +12294,13 @@
         <v>43.632478630000001</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H55" s="6">
         <v>5.9</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J55" s="6">
         <v>1.355</v>
@@ -12491,18 +12312,18 @@
         <v>3</v>
       </c>
       <c r="M55" s="6">
-        <v>0.73908464399999996</v>
+        <v>0.53716285600000002</v>
       </c>
       <c r="N55" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>11</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C56" s="6">
         <v>34.916666999999997</v>
@@ -12541,12 +12362,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>11</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C57" s="6">
         <v>34.916666999999997</v>
@@ -12585,12 +12406,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>11</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58" s="6">
         <v>34.916666999999997</v>
@@ -12629,12 +12450,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>11</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C59" s="6">
         <v>34.916666999999997</v>
@@ -12673,12 +12494,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>12</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C60" s="6">
         <v>26.75</v>
@@ -12717,12 +12538,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C61" s="6">
         <v>26.75</v>
@@ -12761,12 +12582,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>12</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C62" s="6">
         <v>26.75</v>
@@ -12805,12 +12626,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>12</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" s="6">
         <v>26.75</v>
@@ -12849,12 +12670,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>12</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C64" s="6">
         <v>26.75</v>
@@ -12893,12 +12714,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C65" s="6">
         <v>26.75</v>
@@ -12937,12 +12758,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>13</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" s="6">
         <v>39.6</v>
@@ -12963,7 +12784,7 @@
         <v>8.34</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J66" s="6">
         <v>0.16768417930000001</v>
@@ -12981,12 +12802,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>13</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C67" s="6">
         <v>39.6</v>
@@ -13007,7 +12828,7 @@
         <v>8.02</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J67" s="6">
         <v>0.1663919364</v>
@@ -13025,12 +12846,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>13</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68" s="6">
         <v>39.6</v>
@@ -13051,7 +12872,7 @@
         <v>7.9</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J68" s="6">
         <v>0.19271043760000001</v>
@@ -13069,12 +12890,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>13</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C69" s="6">
         <v>43.5</v>
@@ -13095,7 +12916,7 @@
         <v>7.89</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J69" s="6">
         <v>0.2930988276</v>
@@ -13113,12 +12934,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>13</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C70" s="6">
         <v>43.5</v>
@@ -13139,7 +12960,7 @@
         <v>6.65</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J70" s="6">
         <v>0.22637404010000001</v>
@@ -13157,12 +12978,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>13</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C71" s="6">
         <v>43.5</v>
@@ -13183,7 +13004,7 @@
         <v>6.15</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J71" s="6">
         <v>0.29420961030000004</v>
@@ -13201,12 +13022,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>14</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C72" s="6">
         <v>51.55</v>
@@ -13245,12 +13066,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>14</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="6">
         <v>51.55</v>
@@ -13289,12 +13110,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>15</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C74" s="6">
         <v>54.828611000000002</v>
@@ -13333,12 +13154,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>15</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C75" s="6">
         <v>54.828888999999997</v>
@@ -13377,12 +13198,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>15</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C76" s="6">
         <v>54.835000000000001</v>
@@ -13421,12 +13242,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>15</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C77" s="6">
         <v>52.913888999999998</v>
@@ -13465,12 +13286,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>15</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C78" s="6">
         <v>52.981110999999999</v>
@@ -13509,12 +13330,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>15</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C79" s="6">
         <v>52.874443999999997</v>
@@ -13553,12 +13374,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>15</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C80" s="6">
         <v>50.6325</v>
@@ -13597,12 +13418,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>15</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C81" s="6">
         <v>50.598056</v>
@@ -13641,12 +13462,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>15</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C82" s="6">
         <v>50.601111000000003</v>
@@ -13685,12 +13506,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>15</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C83" s="6">
         <v>50.609166999999999</v>
@@ -13729,12 +13550,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>16</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C84" s="6">
         <v>51.816943999999999</v>
@@ -13773,53 +13594,53 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>17</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C85" s="6">
-        <v>44.25</v>
+        <v>48.716667000000001</v>
       </c>
       <c r="D85" s="6">
-        <v>-122.166667</v>
+        <v>9.2166669999999993</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F85" s="6">
-        <v>126.7379679</v>
+        <v>36.649214659999998</v>
       </c>
       <c r="G85" s="6">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H85" s="6">
-        <v>5.5</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>54</v>
+        <v>6.3000001909999996</v>
+      </c>
+      <c r="I85" s="6">
+        <v>12</v>
       </c>
       <c r="J85" s="6">
-        <v>0.30630000000000002</v>
+        <v>0.48685294280000002</v>
       </c>
       <c r="K85" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L85" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M85" s="6">
-        <v>0.76587940099999996</v>
+        <v>0.62457442100000005</v>
       </c>
       <c r="N85" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>14</v>
@@ -13849,68 +13670,68 @@
         <v>0.48685294280000002</v>
       </c>
       <c r="K86" s="9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L86" s="6">
         <v>3</v>
       </c>
       <c r="M86" s="6">
-        <v>0.62457442100000005</v>
+        <v>0.40051805099999999</v>
       </c>
       <c r="N86" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>18</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C87" s="6">
-        <v>48.716667000000001</v>
+        <v>50.35</v>
       </c>
       <c r="D87" s="6">
-        <v>9.2166669999999993</v>
+        <v>9.9333329999999993</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F87" s="6">
-        <v>36.649214659999998</v>
+        <v>64.873417720000006</v>
       </c>
       <c r="G87" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H87" s="6">
-        <v>6.3000001909999996</v>
+        <v>3.9</v>
       </c>
       <c r="I87" s="6">
-        <v>12</v>
+        <v>15.44897959</v>
       </c>
       <c r="J87" s="6">
-        <v>0.48685294280000002</v>
+        <v>1.5593218</v>
       </c>
       <c r="K87" s="9">
-        <v>1000</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="L87" s="6">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="M87" s="6">
-        <v>0.40051805099999999</v>
+        <v>7.5630439999999993E-2</v>
       </c>
       <c r="N87" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C88" s="6">
         <v>50.35</v>
@@ -13928,13 +13749,13 @@
         <v>28</v>
       </c>
       <c r="H88" s="6">
-        <v>3.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I88" s="6">
-        <v>15.44897959</v>
+        <v>14.2</v>
       </c>
       <c r="J88" s="6">
-        <v>1.5593218</v>
+        <v>1.0155930550000001</v>
       </c>
       <c r="K88" s="9">
         <v>7.1999999999999998E-3</v>
@@ -13943,42 +13764,42 @@
         <v>2.75</v>
       </c>
       <c r="M88" s="6">
-        <v>7.5630439999999993E-2</v>
+        <v>7.3964671999999995E-2</v>
       </c>
       <c r="N88" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C89" s="6">
-        <v>50.35</v>
+        <v>52.833333000000003</v>
       </c>
       <c r="D89" s="6">
-        <v>9.9333329999999993</v>
+        <v>10.266667</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F89" s="6">
-        <v>64.873417720000006</v>
+        <v>43.277777780000001</v>
       </c>
       <c r="G89" s="6">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H89" s="6">
-        <v>4.4000000000000004</v>
+        <v>3.7</v>
       </c>
       <c r="I89" s="6">
-        <v>14.2</v>
+        <v>25.17241379</v>
       </c>
       <c r="J89" s="6">
-        <v>1.0155930550000001</v>
+        <v>0.78315849260000003</v>
       </c>
       <c r="K89" s="9">
         <v>7.1999999999999998E-3</v>
@@ -13987,18 +13808,18 @@
         <v>2.75</v>
       </c>
       <c r="M89" s="6">
-        <v>7.3964671999999995E-2</v>
+        <v>5.0343306999999997E-2</v>
       </c>
       <c r="N89" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C90" s="6">
         <v>52.833333000000003</v>
@@ -14016,13 +13837,13 @@
         <v>21</v>
       </c>
       <c r="H90" s="6">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I90" s="6">
-        <v>25.17241379</v>
+        <v>25</v>
       </c>
       <c r="J90" s="6">
-        <v>0.78315849260000003</v>
+        <v>0.24060925800000002</v>
       </c>
       <c r="K90" s="9">
         <v>7.1999999999999998E-3</v>
@@ -14031,13 +13852,13 @@
         <v>2.75</v>
       </c>
       <c r="M90" s="6">
-        <v>5.0343306999999997E-2</v>
+        <v>3.1401116E-2</v>
       </c>
       <c r="N90" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>19</v>
       </c>
@@ -14045,48 +13866,48 @@
         <v>45</v>
       </c>
       <c r="C91" s="6">
-        <v>52.833333000000003</v>
+        <v>51.55</v>
       </c>
       <c r="D91" s="6">
-        <v>10.266667</v>
+        <v>9.8833330000000004</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F91" s="6">
-        <v>43.277777780000001</v>
+        <v>37.978142079999998</v>
       </c>
       <c r="G91" s="6">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H91" s="6">
-        <v>3.9</v>
+        <v>6.5999999049999998</v>
       </c>
       <c r="I91" s="6">
-        <v>25</v>
+        <v>10.53846154</v>
       </c>
       <c r="J91" s="6">
-        <v>0.24060925800000002</v>
+        <v>0.22825140390000001</v>
       </c>
       <c r="K91" s="9">
-        <v>7.1999999999999998E-3</v>
+        <v>20.400000000000002</v>
       </c>
       <c r="L91" s="6">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="M91" s="6">
-        <v>3.1401116E-2</v>
+        <v>0.62599306099999996</v>
       </c>
       <c r="N91" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C92" s="6">
         <v>51.55</v>
@@ -14113,19 +13934,19 @@
         <v>0.22825140390000001</v>
       </c>
       <c r="K92" s="9">
-        <v>20.400000000000002</v>
+        <v>204</v>
       </c>
       <c r="L92" s="6">
         <v>3</v>
       </c>
       <c r="M92" s="6">
-        <v>0.62599306099999996</v>
+        <v>0.51969719599999997</v>
       </c>
       <c r="N92" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>20</v>
       </c>
@@ -14133,43 +13954,43 @@
         <v>46</v>
       </c>
       <c r="C93" s="6">
-        <v>51.55</v>
+        <v>-34.849899999999998</v>
       </c>
       <c r="D93" s="6">
-        <v>9.8833330000000004</v>
+        <v>138.63329999999999</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F93" s="6">
-        <v>37.978142079999998</v>
+        <v>19.962121209999999</v>
       </c>
       <c r="G93" s="6">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H93" s="6">
-        <v>6.5999999049999998</v>
-      </c>
-      <c r="I93" s="6">
-        <v>10.53846154</v>
+        <v>6.9000000950000002</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="J93" s="6">
-        <v>0.22825140390000001</v>
+        <v>0.53102620839999992</v>
       </c>
       <c r="K93" s="9">
-        <v>204</v>
+        <v>1000</v>
       </c>
       <c r="L93" s="6">
         <v>3</v>
       </c>
       <c r="M93" s="6">
-        <v>0.51969719599999997</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="N93" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>21</v>
       </c>
@@ -14177,43 +13998,43 @@
         <v>47</v>
       </c>
       <c r="C94" s="6">
-        <v>-34.849899999999998</v>
+        <v>52.751800000000003</v>
       </c>
       <c r="D94" s="6">
-        <v>138.63329999999999</v>
+        <v>0.39550000000000002</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F94" s="6">
-        <v>19.962121209999999</v>
+        <v>30.205128210000002</v>
       </c>
       <c r="G94" s="6">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H94" s="6">
-        <v>6.9000000950000002</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J94" s="6">
-        <v>0.53102620839999992</v>
+        <v>0.27649200539999996</v>
       </c>
       <c r="K94" s="9">
-        <v>1000</v>
+        <v>10.8</v>
       </c>
       <c r="L94" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M94" s="6">
-        <v>0.57999999999999996</v>
+        <v>0.58333333300000001</v>
       </c>
       <c r="N94" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>22</v>
       </c>
@@ -14221,48 +14042,48 @@
         <v>48</v>
       </c>
       <c r="C95" s="6">
-        <v>52.751800000000003</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="D95" s="6">
-        <v>0.39550000000000002</v>
+        <v>133.816667</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F95" s="6">
-        <v>30.205128210000002</v>
+        <v>117.74891770000001</v>
       </c>
       <c r="G95" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H95" s="6">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="I95" s="6">
+        <v>16.59090909</v>
       </c>
       <c r="J95" s="6">
-        <v>0.27649200539999996</v>
+        <v>0.97030640479999997</v>
       </c>
       <c r="K95" s="9">
-        <v>10.8</v>
+        <v>300</v>
       </c>
       <c r="L95" s="6">
         <v>1</v>
       </c>
       <c r="M95" s="6">
-        <v>0.58333333300000001</v>
+        <v>0.664561662</v>
       </c>
       <c r="N95" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C96" s="6">
         <v>33.799999999999997</v>
@@ -14295,18 +14116,18 @@
         <v>1</v>
       </c>
       <c r="M96" s="6">
-        <v>0.664561662</v>
+        <v>0.63653787100000003</v>
       </c>
       <c r="N96" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C97" s="6">
         <v>33.799999999999997</v>
@@ -14324,13 +14145,13 @@
         <v>31</v>
       </c>
       <c r="H97" s="6">
-        <v>5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I97" s="6">
-        <v>16.59090909</v>
+        <v>19.23076923</v>
       </c>
       <c r="J97" s="6">
-        <v>0.97030640479999997</v>
+        <v>1.4805223410000001</v>
       </c>
       <c r="K97" s="9">
         <v>300</v>
@@ -14339,18 +14160,18 @@
         <v>1</v>
       </c>
       <c r="M97" s="6">
-        <v>0.63653787100000003</v>
+        <v>0.63230018600000004</v>
       </c>
       <c r="N97" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C98" s="6">
         <v>33.799999999999997</v>
@@ -14383,77 +14204,77 @@
         <v>1</v>
       </c>
       <c r="M98" s="6">
-        <v>0.63230018600000004</v>
+        <v>0.65734120699999998</v>
       </c>
       <c r="N98" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>23</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C99" s="6">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D99" s="6">
-        <v>133.816667</v>
+      <c r="C99" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F99" s="6">
-        <v>117.74891770000001</v>
-      </c>
-      <c r="G99" s="6">
-        <v>31</v>
+        <v>12</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="H99" s="6">
-        <v>4.0999999999999996</v>
+        <v>5.47</v>
       </c>
       <c r="I99" s="6">
-        <v>19.23076923</v>
+        <v>9.1333333329999995</v>
       </c>
       <c r="J99" s="6">
-        <v>1.4805223410000001</v>
+        <v>0.2804380622</v>
       </c>
       <c r="K99" s="9">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="L99" s="6">
-        <v>1</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="M99" s="6">
-        <v>0.65734120699999998</v>
+        <v>0.71</v>
       </c>
       <c r="N99" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C100" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G100" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="H100" s="6">
         <v>5.47</v>
@@ -14468,36 +14289,36 @@
         <v>315</v>
       </c>
       <c r="L100" s="6">
-        <v>0.66666666699999999</v>
+        <v>1</v>
       </c>
       <c r="M100" s="6">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="N100" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C101" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G101" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="H101" s="6">
         <v>5.47</v>
@@ -14512,36 +14333,36 @@
         <v>315</v>
       </c>
       <c r="L101" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" s="6">
-        <v>0.69</v>
+        <v>0.74</v>
       </c>
       <c r="N101" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="G102" s="6">
+        <v>20</v>
       </c>
       <c r="H102" s="6">
         <v>5.47</v>
@@ -14556,60 +14377,60 @@
         <v>315</v>
       </c>
       <c r="L102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M102" s="6">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="N102" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>24</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C103" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>54</v>
+      <c r="C103" s="6">
+        <v>35</v>
+      </c>
+      <c r="D103" s="6">
+        <v>114.4</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F103" s="6" t="s">
-        <v>54</v>
+      <c r="F103" s="6">
+        <v>23.870967740000001</v>
       </c>
       <c r="G103" s="6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H103" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="I103" s="6">
-        <v>9.1333333329999995</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="J103" s="6">
-        <v>0.2804380622</v>
+        <v>0.12315749200000001</v>
       </c>
       <c r="K103" s="9">
-        <v>315</v>
+        <v>0.4032</v>
       </c>
       <c r="L103" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M103" s="6">
-        <v>0.72</v>
+        <v>0.79816215400000001</v>
       </c>
       <c r="N103" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>25</v>
       </c>
@@ -14617,72 +14438,72 @@
         <v>51</v>
       </c>
       <c r="C104" s="6">
-        <v>35</v>
+        <v>-37.85</v>
       </c>
       <c r="D104" s="6">
-        <v>114.4</v>
+        <v>176.55</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F104" s="6">
-        <v>23.870967740000001</v>
+        <v>73.47457627</v>
       </c>
       <c r="G104" s="6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H104" s="6">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>54</v>
+        <v>5.72</v>
+      </c>
+      <c r="I104" s="6">
+        <v>15.02040785</v>
       </c>
       <c r="J104" s="6">
-        <v>0.12315749200000001</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="K104" s="9">
-        <v>0.4032</v>
+        <v>1810</v>
       </c>
       <c r="L104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M104" s="6">
-        <v>0.79816215400000001</v>
+        <v>0.16041417199999999</v>
       </c>
       <c r="N104" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C105" s="6">
-        <v>-37.85</v>
+        <v>-37.549999999999997</v>
       </c>
       <c r="D105" s="6">
-        <v>176.55</v>
+        <v>175.91667000000001</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F105" s="6">
-        <v>73.47457627</v>
+        <v>80.083682010000004</v>
       </c>
       <c r="G105" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H105" s="6">
-        <v>5.72</v>
+        <v>5.76</v>
       </c>
       <c r="I105" s="6">
-        <v>15.02040785</v>
+        <v>13.82857186</v>
       </c>
       <c r="J105" s="6">
-        <v>0.89400000000000002</v>
+        <v>1.087</v>
       </c>
       <c r="K105" s="9">
         <v>1810</v>
@@ -14691,42 +14512,42 @@
         <v>3</v>
       </c>
       <c r="M105" s="6">
-        <v>0.16041417199999999</v>
+        <v>0.17676956499999999</v>
       </c>
       <c r="N105" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C106" s="6">
-        <v>-37.549999999999997</v>
+        <v>-37.698766999999997</v>
       </c>
       <c r="D106" s="6">
-        <v>175.91667000000001</v>
+        <v>175.19745800000001</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F106" s="6">
-        <v>80.083682010000004</v>
+        <v>52.780082989999997</v>
       </c>
       <c r="G106" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H106" s="6">
-        <v>5.76</v>
+        <v>5.86</v>
       </c>
       <c r="I106" s="6">
-        <v>13.82857186</v>
+        <v>13.95454522</v>
       </c>
       <c r="J106" s="6">
-        <v>1.087</v>
+        <v>1.1779999999999999</v>
       </c>
       <c r="K106" s="9">
         <v>1810</v>
@@ -14735,42 +14556,42 @@
         <v>3</v>
       </c>
       <c r="M106" s="6">
-        <v>0.17676956499999999</v>
+        <v>0.196681306</v>
       </c>
       <c r="N106" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C107" s="6">
-        <v>-37.698766999999997</v>
+        <v>-38.183331000000003</v>
       </c>
       <c r="D107" s="6">
-        <v>175.19745800000001</v>
+        <v>175.19972200000001</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F107" s="6">
-        <v>52.780082989999997</v>
+        <v>65.361702129999998</v>
       </c>
       <c r="G107" s="6">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H107" s="6">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="I107" s="6">
-        <v>13.95454522</v>
+        <v>8.7765957449999998</v>
       </c>
       <c r="J107" s="6">
-        <v>1.1779999999999999</v>
+        <v>1.6539999999999999</v>
       </c>
       <c r="K107" s="9">
         <v>1810</v>
@@ -14779,13 +14600,13 @@
         <v>3</v>
       </c>
       <c r="M107" s="6">
-        <v>0.196681306</v>
+        <v>0.20668128599999999</v>
       </c>
       <c r="N107" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>26</v>
       </c>
@@ -14793,48 +14614,48 @@
         <v>52</v>
       </c>
       <c r="C108" s="6">
-        <v>-38.183331000000003</v>
+        <v>55.116388999999998</v>
       </c>
       <c r="D108" s="6">
-        <v>175.19972200000001</v>
+        <v>-5</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F108" s="6">
-        <v>65.361702129999998</v>
+        <v>72.222222220000006</v>
       </c>
       <c r="G108" s="6">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H108" s="6">
-        <v>5.78</v>
+        <v>5.24</v>
       </c>
       <c r="I108" s="6">
-        <v>8.7765957449999998</v>
+        <v>11.945701359999999</v>
       </c>
       <c r="J108" s="6">
-        <v>1.6539999999999999</v>
+        <v>1.421</v>
       </c>
       <c r="K108" s="9">
-        <v>1810</v>
+        <v>2080</v>
       </c>
       <c r="L108" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M108" s="6">
-        <v>0.20668128599999999</v>
+        <v>0.64893818000000003</v>
       </c>
       <c r="N108" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C109" s="6">
         <v>55.116388999999998</v>
@@ -14852,13 +14673,13 @@
         <v>20</v>
       </c>
       <c r="H109" s="6">
-        <v>5.24</v>
+        <v>5</v>
       </c>
       <c r="I109" s="6">
-        <v>11.945701359999999</v>
+        <v>11.4375</v>
       </c>
       <c r="J109" s="6">
-        <v>1.421</v>
+        <v>1.087</v>
       </c>
       <c r="K109" s="9">
         <v>2080</v>
@@ -14867,57 +14688,14 @@
         <v>2</v>
       </c>
       <c r="M109" s="6">
-        <v>0.64893818000000003</v>
+        <v>0.48497974799999999</v>
       </c>
       <c r="N109" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
-        <v>27</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C110" s="6">
-        <v>55.116388999999998</v>
-      </c>
-      <c r="D110" s="6">
-        <v>-5</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="6">
-        <v>72.222222220000006</v>
-      </c>
-      <c r="G110" s="6">
-        <v>20</v>
-      </c>
-      <c r="H110" s="6">
-        <v>5</v>
-      </c>
-      <c r="I110" s="6">
-        <v>11.4375</v>
-      </c>
-      <c r="J110" s="6">
-        <v>1.087</v>
-      </c>
-      <c r="K110" s="9">
-        <v>2080</v>
-      </c>
-      <c r="L110" s="6">
-        <v>2</v>
-      </c>
-      <c r="M110" s="6">
-        <v>0.48497974799999999</v>
-      </c>
-      <c r="N110" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:N109" xr:uid="{63F238F5-6035-4E09-8303-55A8A0E9A5B8}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
